--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-06-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-06-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>חן כהן – תל גיבורים</v>
+        <v>אנוש ilnka x – קרבית</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%97%d7%9f-%d7%9b%d7%94%d7%9f-%d7%aa%d7%9c-%d7%92%d7%99%d7%91%d7%95%d7%a8%d7%99%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%90%d7%a0%d7%95%d7%a9-ilnka-x-%d7%a7%d7%a8%d7%91%d7%99%d7%aa/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>תל גיבורים" של  חן כהן הוא שיר חשוף  כואב ומזכך. זהו מסע בזמן אל מחוזות הילדות וההתבגרות בשכונת תל גיבורים בחולון, שעיקרו הוא מסע פנימי אל נבכי דימוי הגוף, החרדה והחיפוש העיקש אחר קבלה עצמית ו"בית" בתוך הנפש. הטקסט והמוזיקה</v>
+        <v>השיר "קרבית" של אנוש צוברי (באירוח ilanka, המגולמת על ידי השחקן והרקדן אילן זכרוב) הוא אחת היצירות המטורללות, המבריקות והאמיצות ביותר שידע הפופ הים-תיכוני בישראל. קל לפטור את השיר כרצועת דאנס-חפלה מועדונים קלילה המיועדת להרמות. אולם, "קרבית" הוא למעשה שיר</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,50 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>חן כהן – תל גיבורים</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>סהראת – שמש כחולה</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-06-08</v>
-      </c>
-      <c r="C3" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%94%d7%a8%d7%90%d7%aa-%d7%a9%d7%9e%d7%a9-%d7%9b%d7%97%d7%95%d7%9c%d7%94/</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-06-08</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v>השיר "שמש כחולה" של להקת "סהראת" בביצועה של אורטל חאיק פינקל, הוא יצירה מקורית יוצאת דופן בנוף המוזיקלי המקומי. השיר, שנכתב על ידי מקימת ההרכב אתי נאור והולחן על ידי אדיר לוי, מביא  חשיפה רגשית  המטופלת ברגישות ובעוצמה יוצאת דופן.</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>סהראת – שמש כחולה</v>
+        <v>אנוש ilnka x – קרבית</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-06-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-06-week02/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אנוש ilnka x – קרבית</v>
+        <v>עדן בן זקן וששון איפרם שאולוב מחול</v>
       </c>
       <c r="B2" t="str">
         <v>2026-06-09</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%a0%d7%95%d7%a9-ilnka-x-%d7%a7%d7%a8%d7%91%d7%99%d7%aa/</v>
+        <v>https://yosmusic.com/%d7%a2%d7%93%d7%9f-%d7%91%d7%9f-%d7%96%d7%a7%d7%9f-%d7%95%d7%a9%d7%a9%d7%95%d7%9f-%d7%90%d7%99%d7%a4%d7%a8%d7%9d-%d7%a9%d7%90%d7%95%d7%9c%d7%95%d7%91-%d7%9e%d7%97%d7%95%d7%9c/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-06-09</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "קרבית" של אנוש צוברי (באירוח ilanka, המגולמת על ידי השחקן והרקדן אילן זכרוב) הוא אחת היצירות המטורללות, המבריקות והאמיצות ביותר שידע הפופ הים-תיכוני בישראל. קל לפטור את השיר כרצועת דאנס-חפלה מועדונים קלילה המיועדת להרמות. אולם, "קרבית" הוא למעשה שיר</v>
+        <v>הדואט "מחול" של עדן בן זקן וששון איפרם שאולוב מספק הצצה  למנגנון התעשייתי המשומן של המוזיקה הים-תיכונית העכשווית, ומציג את מה שניתן לכנות "נוסחת הזהב" של הפופ המקומי: טקסט פשטני, מנגינה מלנכולית ושירה מלודרמטית. הטקסט של השיר פונה למכנה המשותף</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אנוש ilnka x – קרבית</v>
+        <v>עדן בן זקן וששון איפרם שאולוב מחול</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-06-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-06-week02/titles.xlsx
@@ -436,7 +436,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עדן בן זקן וששון איפרם שאולוב מחול</v>
+        <v>עדן בן זקן וששון איפרם שאולוב – מחול</v>
       </c>
       <c r="B2" t="str">
         <v>2026-06-09</v>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עדן בן זקן וששון איפרם שאולוב מחול</v>
+        <v>עדן בן זקן וששון איפרם שאולוב – מחול</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-06-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-06-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עדן בן זקן וששון איפרם שאולוב – מחול</v>
+        <v>התקווה וסבא אורי (תמיר בר) 6 – מכת זקנה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a2%d7%93%d7%9f-%d7%91%d7%9f-%d7%96%d7%a7%d7%9f-%d7%95%d7%a9%d7%a9%d7%95%d7%9f-%d7%90%d7%99%d7%a4%d7%a8%d7%9d-%d7%a9%d7%90%d7%95%d7%9c%d7%95%d7%91-%d7%9e%d7%97%d7%95%d7%9c/</v>
+        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-%d7%95%d7%a1%d7%91%d7%90-%d7%90%d7%95%d7%a8%d7%99-%d7%aa%d7%9e%d7%99%d7%a8-%d7%91%d7%a8-6-%d7%9e%d7%9b%d7%aa-%d7%96%d7%a7%d7%a0%d7%94/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הדואט "מחול" של עדן בן זקן וששון איפרם שאולוב מספק הצצה  למנגנון התעשייתי המשומן של המוזיקה הים-תיכונית העכשווית, ומציג את מה שניתן לכנות "נוסחת הזהב" של הפופ המקומי: טקסט פשטני, מנגינה מלנכולית ושירה מלודרמטית. הטקסט של השיר פונה למכנה המשותף</v>
+        <v>הניסיון לחבר בין מוזיקת הרגאיי הקלילה והקצבית של להקת "התקווה 6" לבין ההומור הנונסנסי והדמות האייקונית של "סבא אורי" (בגילומו של תמיר בר) מתגלה כפספוס. השיר אמנם מנסה להצחיק ולייצר מניפסט משעשע על משבר גיל ה-40 והזקנה, אך הוא נופל</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,88 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עדן בן זקן וששון איפרם שאולוב – מחול</v>
+        <v>התקווה וסבא אורי (תמיר בר) 6 – מכת זקנה</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>נס X סטילה – מי כמוני</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="C3" t="str">
+        <v>https://yosmusic.com/%d7%a0%d7%a1-x-%d7%a1%d7%98%d7%99%d7%9c%d7%94-%d7%9e%d7%99-%d7%9b%d7%9e%d7%95%d7%a0%d7%99/</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>"מי כמוני" הוא יריית פתיחה לקראת הפרויקט החדש של הצמד נס וסטילה. השיר מביא את כל מה שהפך אותם לאחד הצמדים המסקרנים והמזוהים ביותר בהיפ־הופ הישראלי של השנים האחרונות: ביטים קופצניים, הומור פרוע, ביטחון עצמי מוגזם במכוון, ושפה שמרגישה כאילו</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>נס X סטילה – מי כמוני</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>מיוז Nightshift Superstar</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="C4" t="str">
+        <v>https://yosmusic.com/%d7%9e%d7%99%d7%95%d7%96-nightshift-superstar/</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v>"Nightshift Superstar" הוא אחד השירים המפתיעים ביותר של Muse בשנים האחרונות. בעוד שהלהקה מזוהה בדרך כלל עם רוק חללי, פרוגרסיבי ודרמטי, כאן היא פונה לטריטוריה הרבה יותר רקידה: שילוב של French House, דיסקו מודרני, פאנק אלקטרוני ורוק אצטדיונים. השיר הוא</v>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>מיוז Nightshift Superstar</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-06-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-06-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>התקווה וסבא אורי (תמיר בר) 6 – מכת זקנה</v>
+        <v>עדן חסון הלוואי שטוב לך</v>
       </c>
       <c r="B2" t="str">
         <v>2026-06-10</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-%d7%95%d7%a1%d7%91%d7%90-%d7%90%d7%95%d7%a8%d7%99-%d7%aa%d7%9e%d7%99%d7%a8-%d7%91%d7%a8-6-%d7%9e%d7%9b%d7%aa-%d7%96%d7%a7%d7%a0%d7%94/</v>
+        <v>https://yosmusic.com/%d7%a2%d7%93%d7%9f-%d7%97%d7%a1%d7%95%d7%9f-%d7%94%d7%9c%d7%95%d7%95%d7%90%d7%99-%d7%a9%d7%98%d7%95%d7%91-%d7%9c%d7%9a/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-06-10</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הניסיון לחבר בין מוזיקת הרגאיי הקלילה והקצבית של להקת "התקווה 6" לבין ההומור הנונסנסי והדמות האייקונית של "סבא אורי" (בגילומו של תמיר בר) מתגלה כפספוס. השיר אמנם מנסה להצחיק ולייצר מניפסט משעשע על משבר גיל ה-40 והזקנה, אך הוא נופל</v>
+        <v>השיר "הלוואי שטוב לך" של עדן חסון הוא דוגמה מובהקת לנוסחת שחסון מאמץ כנוסחה בטוחה  – שילוב מדויק בין פופ ים-תיכוני עדכני, טקסטים על לבבות שבורים , ומלודרמה רגשית בסלסול מלנכולי דשמטרתה לדבר אל הלב של הקהל הרחב. השיר בנוי</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,88 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>התקווה וסבא אורי (תמיר בר) 6 – מכת זקנה</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>נס X סטילה – מי כמוני</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-06-10</v>
-      </c>
-      <c r="C3" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%a1-x-%d7%a1%d7%98%d7%99%d7%9c%d7%94-%d7%9e%d7%99-%d7%9b%d7%9e%d7%95%d7%a0%d7%99/</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-06-10</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v>"מי כמוני" הוא יריית פתיחה לקראת הפרויקט החדש של הצמד נס וסטילה. השיר מביא את כל מה שהפך אותם לאחד הצמדים המסקרנים והמזוהים ביותר בהיפ־הופ הישראלי של השנים האחרונות: ביטים קופצניים, הומור פרוע, ביטחון עצמי מוגזם במכוון, ושפה שמרגישה כאילו</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>נס X סטילה – מי כמוני</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>מיוז Nightshift Superstar</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-06-10</v>
-      </c>
-      <c r="C4" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%99%d7%95%d7%96-nightshift-superstar/</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-06-10</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v>"Nightshift Superstar" הוא אחד השירים המפתיעים ביותר של Muse בשנים האחרונות. בעוד שהלהקה מזוהה בדרך כלל עם רוק חללי, פרוגרסיבי ודרמטי, כאן היא פונה לטריטוריה הרבה יותר רקידה: שילוב של French House, דיסקו מודרני, פאנק אלקטרוני ורוק אצטדיונים. השיר הוא</v>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>מיוז Nightshift Superstar</v>
+        <v>עדן חסון הלוואי שטוב לך</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-06-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-06-week02/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עדן חסון הלוואי שטוב לך</v>
+        <v>בניה ברבי – לילה טוב</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a2%d7%93%d7%9f-%d7%97%d7%a1%d7%95%d7%9f-%d7%94%d7%9c%d7%95%d7%95%d7%90%d7%99-%d7%a9%d7%98%d7%95%d7%91-%d7%9c%d7%9a/</v>
+        <v>https://yosmusic.com/%d7%91%d7%a0%d7%99%d7%94-%d7%91%d7%a8%d7%91%d7%99-%d7%9c%d7%99%d7%9c%d7%94-%d7%98%d7%95%d7%91/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "הלוואי שטוב לך" של עדן חסון הוא דוגמה מובהקת לנוסחת שחסון מאמץ כנוסחה בטוחה  – שילוב מדויק בין פופ ים-תיכוני עדכני, טקסטים על לבבות שבורים , ומלודרמה רגשית בסלסול מלנכולי דשמטרתה לדבר אל הלב של הקהל הרחב. השיר בנוי</v>
+        <v>השיר "לילה טוב" ששר בניה ברבי, הוא הצצה כנה, לעיתים מכאיבה, אל תוך הנפש של מי שנמצא במרכז הבמה, אך חש צורך לברוח מהרעש ולהתמודד עם השקט. זהו שיר שמייצג את המציאות של לא מעט אמנים בתעשייה, הנקרעים בין אור</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עדן חסון הלוואי שטוב לך</v>
+        <v>בניה ברבי – לילה טוב</v>
       </c>
     </row>
   </sheetData>
